--- a/backend/scripts/Capsicum prices.xlsx
+++ b/backend/scripts/Capsicum prices.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Final year Project\Smart-Polytunnel-Cultivation-Advisory-and-Management-Web-Platform\backend\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3878FCA1-45E4-4CB9-8815-45CA014AF7CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48605777-7DE0-4F7E-994D-1A0A65C5D546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C81B32F8-3906-482E-AF5F-75AA66878329}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="5">
   <si>
     <t>Date Column</t>
   </si>
@@ -435,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9624FD8-D51E-4276-ACF3-532B5786DCA6}">
-  <dimension ref="A1:D362"/>
+  <dimension ref="A1:D367"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
@@ -5505,6 +5505,72 @@
       <c r="B362" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="C362">
+        <v>190</v>
+      </c>
+      <c r="D362">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A363" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C363">
+        <v>250</v>
+      </c>
+      <c r="D363">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A364" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C364">
+        <v>300</v>
+      </c>
+      <c r="D364">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A365" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C365">
+        <v>350</v>
+      </c>
+      <c r="D365">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A366" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C366">
+        <v>350</v>
+      </c>
+      <c r="D366">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A367" s="1"/>
+      <c r="B367" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
